--- a/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/05_Ürün Güvenliği, Mevzuat ve Sorumluluk/EKG-KLT-FRM-05_malzeme_uygunluk_beyani_reach__elv_ve_imds_kaydi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/05_Ürün Güvenliği, Mevzuat ve Sorumluluk/EKG-KLT-FRM-05_malzeme_uygunluk_beyani_reach__elv_ve_imds_kaydi.xlsx
@@ -937,7 +937,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-05&amp;C&amp;"Arial,Regular"&amp;11Malzeme Uygunluk Beyanı (REACH / ELV) ve IMDS Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 14.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41b04fc1150646ff"/>
   <x:tableParts count="1">
@@ -1206,7 +1207,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-05&amp;C&amp;"Arial,Regular"&amp;11Malzeme Uygunluk Beyanı (REACH / ELV) ve IMDS Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 14.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33fde71328d14a54"/>
   <x:tableParts count="1">
@@ -1518,7 +1520,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-05&amp;C&amp;"Arial,Regular"&amp;11Malzeme Uygunluk Beyanı (REACH / ELV) ve IMDS Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 14.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R562122e36d7f4569"/>
   <x:tableParts count="1">
@@ -1688,7 +1691,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-05&amp;C&amp;"Arial,Regular"&amp;11Malzeme Uygunluk Beyanı (REACH / ELV) ve IMDS Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 14.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ebe552f436f4ebe"/>
   <x:tableParts count="1">
